--- a/과제질문.xlsx
+++ b/과제질문.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="추가질문(판매담당자 예시)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="예상질문_경우의수50" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -56,8 +57,12 @@
     <font>
       <name val="Arial"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +73,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCEEDD"/>
+        <bgColor rgb="00FCEEDD"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,7 +96,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -96,6 +107,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1395,4 +1409,378 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" style="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>예상 질문 (분류 없음, 다양한 경우의 수 고려 50개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>SS400 두께 15T, 폭 2100, 길이 5500 규격에 맞나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>AH36 최대 투입 가능 두께가 몇 T예요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>EH36 강종이 기준표에 등록되어 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>X65 강종 광양에서 생산 가능한가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>HSB460 여재 재고 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>C170150PG201 출강목표로 몇 톤 남았어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>지난달 AH36 60톤 투입했는데 이번에 30톤 추가 가능한가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ORD-2026-0002 주문 지금 어디까지 진행됐어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>이 주문 압연 완료 예정일이 언제예요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>소LOT 기준 톤수가 정확히 몇 톤이에요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>데일리 집약은 무슨 조건이 있어야 되나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>01SA490210 주문서 80톤인데 투입 가능해요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>신규 주문(주문서 없음)으로 SS400 60톤 넣어도 될까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>460MLO 강종 83T 규격 기준이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>건축용 POSTEN, 아직 품질설계 전인데 사이즈 기준 확인 가능해요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TMCP강 두께 120T 기준이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>두께 25T 폭 2500 길이 8000이면 단중이 얼마나 나와요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>ORD-2026-0004 규격 기준으로 단중 계산해줄 수 있어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>AH36 90T 열처리재인데 투입 가능 구간이 어떻게 돼요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>EN-S355NL 열처리 여부에 따라 기준이 달라지나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>광양이랑 포항 최대 두께 차이가 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>포항 최소 길이 제약이 어떻게 되나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>수출용 규격은 내수용이랑 사이즈 기준이 다른가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>C090120PG105 출강목표 재고 있어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>C080155L5201 출강목표로 20톤 추가 커버 가능한가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>이 조합으로 설계 가능성이 있을까요? (참고용으로 알려주세요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>이 주문이 확인필요로 나온 이유가 뭐예요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>AH36이랑 SS400 중에 이 규격에 더 적합한 강종이 뭐예요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>실제 압연 손실 감안하면 이 주문 단중이 얼마나 나올까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>이 조합 설계로 최종 확정해도 되나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>이 문의 다음 주까지 답변 가능할까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>긴급 문의인데 AH36 20톤 오늘 안에 투입 가능 여부 확인 가능해요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>API X70 규격 처음 문의하는데 기준이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>SN490B 건축용 규격 투입 이력이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>조선용이랑 건축용은 사이즈 기준이 다르게 적용되나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>이 강종 예비품질설계 결과가 나와 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>여재slab 재고가 0인 경우 대안이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>ORD-2026-0001 주문 규격이랑 여재slab 매칭되나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>진행 중인 주문들 중에 이번 주 압연 예정인 게 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>아까 답변이 틀린 것 같은데 다시 확인해줄 수 있어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>이 문의는 사이즈 기준이랑 여재 둘 다 관련된 건데 한 번에 확인 가능해요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>두께 5T처럼 너무 얇은 규격도 기준이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>두께 250T 같은 극후물도 기준표에 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>이 규격, 여러 제철소 중에 어디가 재고가 더 많아요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>소LOT으로 판정되면 그다음엔 어떻게 처리되나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>데일리 집약 대상인지 아닌지는 최종적으로 누가 판단하나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>이번 주문이 예전 이력이랑 완전히 똑같은 규격인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>강종만 알고 두께/폭/길이를 모르는데 기준 확인이 가능한가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>조합 설계 참고의견을 받으면 저희가 뭘 더 준비해야 하나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>후판 말고 코일 같은 다른 제품도 이 챗봇에서 문의 가능한가요?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>